--- a/data/trans_orig/P2A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2007</t>
+          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>310728</t>
+          <t>308637</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>362990</t>
+          <t>364262</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>408377</t>
+          <t>409157</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>455841</t>
+          <t>460426</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>734314</t>
+          <t>737037</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>807038</t>
+          <t>805344</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,26%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>331022</t>
+          <t>329750</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>383284</t>
+          <t>385375</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>232510</t>
+          <t>227925</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>279974</t>
+          <t>279194</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>575325</t>
+          <t>577019</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>648049</t>
+          <t>645326</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,68%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>437976</t>
+          <t>435150</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>499956</t>
+          <t>497966</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>600914</t>
+          <t>600389</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>659614</t>
+          <t>662363</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1057414</t>
+          <t>1056142</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1145059</t>
+          <t>1141980</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,16%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>461844</t>
+          <t>463834</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>523824</t>
+          <t>526650</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>308779</t>
+          <t>306030</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>367479</t>
+          <t>368004</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>785134</t>
+          <t>788213</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>872779</t>
+          <t>874051</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,28%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>306371</t>
+          <t>308752</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>360027</t>
+          <t>360595</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>411672</t>
+          <t>409990</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>461619</t>
+          <t>459154</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>732848</t>
+          <t>734462</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>807226</t>
+          <t>809810</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,44%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>318482</t>
+          <t>317914</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>372138</t>
+          <t>369757</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>222222</t>
+          <t>224687</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>272169</t>
+          <t>273851</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>555124</t>
+          <t>552540</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>629502</t>
+          <t>627888</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,09%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>407957</t>
+          <t>410052</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>468301</t>
+          <t>469224</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>626819</t>
+          <t>621910</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>690102</t>
+          <t>687754</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1053860</t>
+          <t>1048611</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1140327</t>
+          <t>1138298</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,47%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>473921</t>
+          <t>472998</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>534265</t>
+          <t>532170</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348510</t>
+          <t>350858</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>411793</t>
+          <t>416702</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>840507</t>
+          <t>842536</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>926974</t>
+          <t>932223</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>47,06%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1519872</t>
+          <t>1520616</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1638673</t>
+          <t>1636835</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2100896</t>
+          <t>2105314</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2222608</t>
+          <t>2214989</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3652324</t>
+          <t>3655098</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3821214</t>
+          <t>3821684</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1637870</t>
+          <t>1639708</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1756671</t>
+          <t>1755927</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1156589</t>
+          <t>1164208</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1278301</t>
+          <t>1273883</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2834527</t>
+          <t>2834057</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3003417</t>
+          <t>3000643</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,08%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2012</t>
+          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>400406</t>
+          <t>398779</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>450557</t>
+          <t>451848</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>454092</t>
+          <t>452926</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>505842</t>
+          <t>504629</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>869384</t>
+          <t>870207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>940697</t>
+          <t>946130</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,56%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>252912</t>
+          <t>251621</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>303063</t>
+          <t>304690</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>191208</t>
+          <t>192421</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>242958</t>
+          <t>244124</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>459822</t>
+          <t>454389</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>531135</t>
+          <t>530312</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,87%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>521916</t>
+          <t>520121</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>584594</t>
+          <t>584564</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>706176</t>
+          <t>700743</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>766154</t>
+          <t>764296</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1240068</t>
+          <t>1241107</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1333911</t>
+          <t>1333129</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,03%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>433353</t>
+          <t>433383</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>496031</t>
+          <t>497826</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>266030</t>
+          <t>267888</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>326008</t>
+          <t>331441</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>716220</t>
+          <t>717002</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>810063</t>
+          <t>809024</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,46%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>351302</t>
+          <t>350128</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>407897</t>
+          <t>409966</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>497673</t>
+          <t>498971</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>550667</t>
+          <t>550387</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>864048</t>
+          <t>869752</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>944540</t>
+          <t>949109</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,84%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>349726</t>
+          <t>347657</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>406321</t>
+          <t>407495</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226507</t>
+          <t>226787</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>279501</t>
+          <t>278203</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>590257</t>
+          <t>585688</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>670749</t>
+          <t>665045</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>517682</t>
+          <t>514485</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>579616</t>
+          <t>576712</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>689746</t>
+          <t>689400</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>751355</t>
+          <t>751385</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,47 +3759,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>65,54%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>71,43%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1268455</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>1221093</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>1311133</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>63,43%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>61,07%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>65,57%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>71,43%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1202</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1268455</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1225261</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1311379</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>63,43%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>61,27%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>368123</t>
+          <t>371027</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>430057</t>
+          <t>433254</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>300546</t>
+          <t>300516</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362155</t>
+          <t>362501</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3877,42 +3877,42 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>34,46%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>731185</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>688507</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>778547</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>36,57%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>34,43%</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>711</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>731185</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>688261</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>774379</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>36,57%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>34,42%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,93%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1849476</t>
+          <t>1850019</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1968067</t>
+          <t>1965044</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2403543</t>
+          <t>2409124</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2519341</t>
+          <t>2519358</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4285196</t>
+          <t>4292739</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4452118</t>
+          <t>4457638</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,82%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1458712</t>
+          <t>1461735</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1577303</t>
+          <t>1576760</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1038968</t>
+          <t>1038951</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1154766</t>
+          <t>1149185</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2532970</t>
+          <t>2527450</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2699892</t>
+          <t>2692349</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2016</t>
+          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>329589</t>
+          <t>331525</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>383674</t>
+          <t>385093</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>413204</t>
+          <t>415093</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>462719</t>
+          <t>465442</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>762655</t>
+          <t>762039</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>835174</t>
+          <t>835145</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>291126</t>
+          <t>289707</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>345211</t>
+          <t>343275</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>210120</t>
+          <t>207397</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259635</t>
+          <t>257746</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>512465</t>
+          <t>512494</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>584984</t>
+          <t>585600</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,45%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>494580</t>
+          <t>498445</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>559590</t>
+          <t>563291</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>653415</t>
+          <t>651986</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>713192</t>
+          <t>716049</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1166831</t>
+          <t>1166354</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1260274</t>
+          <t>1256625</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,84%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>462841</t>
+          <t>459140</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>527851</t>
+          <t>523986</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>329721</t>
+          <t>326864</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>389498</t>
+          <t>390927</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>805070</t>
+          <t>808719</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>898513</t>
+          <t>898990</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,53%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>341370</t>
+          <t>339964</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>400636</t>
+          <t>398466</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>443159</t>
+          <t>443761</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>500724</t>
+          <t>499972</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>803803</t>
+          <t>799650</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>884577</t>
+          <t>878556</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>56,88%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>358916</t>
+          <t>361086</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>418182</t>
+          <t>419588</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>284287</t>
+          <t>285039</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>341852</t>
+          <t>341250</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>659986</t>
+          <t>666007</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>740760</t>
+          <t>744913</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,23%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>488628</t>
+          <t>490550</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>548105</t>
+          <t>547475</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>629423</t>
+          <t>629484</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>692434</t>
+          <t>694785</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1136745</t>
+          <t>1136241</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1225110</t>
+          <t>1222061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,68%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>389462</t>
+          <t>390092</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>448939</t>
+          <t>447017</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>351345</t>
+          <t>348994</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>414356</t>
+          <t>414295</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>756236</t>
+          <t>759285</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>844601</t>
+          <t>845105</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,65%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1712701</t>
+          <t>1714718</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1832928</t>
+          <t>1829476</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2202021</t>
+          <t>2204921</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2314803</t>
+          <t>2318325</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3949120</t>
+          <t>3954961</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4116959</t>
+          <t>4114052</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,29%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1561422</t>
+          <t>1564874</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1681649</t>
+          <t>1679632</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1229739</t>
+          <t>1226217</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1342521</t>
+          <t>1339621</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2821933</t>
+          <t>2824840</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2989772</t>
+          <t>2983931</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2023</t>
+          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>255916</t>
+          <t>258070</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>311618</t>
+          <t>313631</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>249924</t>
+          <t>261082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>362229</t>
+          <t>363125</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>538317</t>
+          <t>541519</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>656469</t>
+          <t>656008</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,21%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>323823</t>
+          <t>321810</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>379525</t>
+          <t>377371</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>363101</t>
+          <t>362205</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>475406</t>
+          <t>464248</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>704303</t>
+          <t>704764</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>822455</t>
+          <t>819253</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,2%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>213344</t>
+          <t>181488</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>505142</t>
+          <t>503370</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>446744</t>
+          <t>447500</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>500387</t>
+          <t>502155</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>573066</t>
+          <t>576241</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>990756</t>
+          <t>987734</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,91%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>687722</t>
+          <t>689494</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>979520</t>
+          <t>1011376</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>458264</t>
+          <t>456496</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511907</t>
+          <t>511151</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1160760</t>
+          <t>1163782</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1578450</t>
+          <t>1575275</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,22%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>255219</t>
+          <t>260277</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>320441</t>
+          <t>318375</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>377836</t>
+          <t>372261</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>704418</t>
+          <t>717153</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>665910</t>
+          <t>658842</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1080693</t>
+          <t>1073526</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,54%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>384239</t>
+          <t>386305</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>449461</t>
+          <t>444403</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>228948</t>
+          <t>216213</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>555530</t>
+          <t>561105</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>557353</t>
+          <t>564520</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>972136</t>
+          <t>979204</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,78%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>320382</t>
+          <t>324603</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>386343</t>
+          <t>388349</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>372735</t>
+          <t>379906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>506020</t>
+          <t>511462</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>719221</t>
+          <t>723580</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>871687</t>
+          <t>873317</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,2%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>540488</t>
+          <t>538482</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>606449</t>
+          <t>602228</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>588912</t>
+          <t>583470</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>722197</t>
+          <t>715026</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1150076</t>
+          <t>1148446</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1302542</t>
+          <t>1298183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,21%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1045718</t>
+          <t>1022275</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1448031</t>
+          <t>1443659</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1639887</t>
+          <t>1633608</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2155738</t>
+          <t>2158123</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2816485</t>
+          <t>2822782</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3464703</t>
+          <t>3424282</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>47,74%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2011786</t>
+          <t>2016158</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2414099</t>
+          <t>2437542</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1556542</t>
+          <t>1554157</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2072393</t>
+          <t>2078672</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3707394</t>
+          <t>3747815</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4355612</t>
+          <t>4349315</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,64%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>308637</t>
+          <t>311451</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>364262</t>
+          <t>363450</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>409157</t>
+          <t>408522</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>460426</t>
+          <t>456927</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>737037</t>
+          <t>730913</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>805344</t>
+          <t>804762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,22%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>329750</t>
+          <t>330562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>385375</t>
+          <t>382561</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>227925</t>
+          <t>231424</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>279194</t>
+          <t>279829</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>577019</t>
+          <t>577601</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>645326</t>
+          <t>651450</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>47,13%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>435150</t>
+          <t>435201</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>497966</t>
+          <t>502082</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>600389</t>
+          <t>600509</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>662363</t>
+          <t>661815</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1056142</t>
+          <t>1058493</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1141980</t>
+          <t>1145308</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,34%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>463834</t>
+          <t>459718</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>526650</t>
+          <t>526599</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>306030</t>
+          <t>306578</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368004</t>
+          <t>367884</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>788213</t>
+          <t>784885</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>874051</t>
+          <t>871700</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,16%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>308752</t>
+          <t>306902</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>360595</t>
+          <t>361990</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>409990</t>
+          <t>409809</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>459154</t>
+          <t>458994</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>734462</t>
+          <t>731204</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>809810</t>
+          <t>807523</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,27%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>317914</t>
+          <t>316519</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>369757</t>
+          <t>371607</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>224687</t>
+          <t>224847</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>273851</t>
+          <t>274032</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>552540</t>
+          <t>554827</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>627888</t>
+          <t>631146</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,33%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>410052</t>
+          <t>407459</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>469224</t>
+          <t>466706</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>621910</t>
+          <t>623820</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>687754</t>
+          <t>687299</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1048611</t>
+          <t>1051989</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1138298</t>
+          <t>1137007</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,4%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>472998</t>
+          <t>475516</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>532170</t>
+          <t>534763</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>350858</t>
+          <t>351313</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>416702</t>
+          <t>414792</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>842536</t>
+          <t>843827</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>932223</t>
+          <t>928845</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,89%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1520616</t>
+          <t>1523547</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1636835</t>
+          <t>1639290</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2105314</t>
+          <t>2098769</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2214989</t>
+          <t>2211245</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3655098</t>
+          <t>3649928</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3821684</t>
+          <t>3815091</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,32%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1639708</t>
+          <t>1637253</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1755927</t>
+          <t>1752996</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1164208</t>
+          <t>1167952</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1273883</t>
+          <t>1280428</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2834057</t>
+          <t>2840650</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3000643</t>
+          <t>3005813</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,16%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>398779</t>
+          <t>397057</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>451848</t>
+          <t>450330</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>452926</t>
+          <t>455989</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>504629</t>
+          <t>506415</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>870207</t>
+          <t>872180</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>946130</t>
+          <t>946577</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,59%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>251621</t>
+          <t>253139</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>304690</t>
+          <t>306412</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>192421</t>
+          <t>190635</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>244124</t>
+          <t>241061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>454389</t>
+          <t>453942</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>530312</t>
+          <t>528339</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,72%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>520121</t>
+          <t>519275</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>584564</t>
+          <t>587764</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>700743</t>
+          <t>703917</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>764296</t>
+          <t>764521</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1241107</t>
+          <t>1241620</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1333129</t>
+          <t>1330245</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,89%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>433383</t>
+          <t>430183</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>497826</t>
+          <t>498672</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>267888</t>
+          <t>267663</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>331441</t>
+          <t>328267</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>717002</t>
+          <t>719886</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>809024</t>
+          <t>808511</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,44%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>350128</t>
+          <t>351599</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>409966</t>
+          <t>408665</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>498971</t>
+          <t>497972</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>550387</t>
+          <t>550662</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>869752</t>
+          <t>864350</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>949109</t>
+          <t>947312</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,72%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>347657</t>
+          <t>348958</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>407495</t>
+          <t>406024</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226787</t>
+          <t>226512</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>278203</t>
+          <t>279202</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>585688</t>
+          <t>587485</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>665045</t>
+          <t>670447</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>514485</t>
+          <t>516745</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>576712</t>
+          <t>578901</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>689400</t>
+          <t>690340</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>751385</t>
+          <t>750045</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1221093</t>
+          <t>1228292</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1311133</t>
+          <t>1312456</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,63%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>371027</t>
+          <t>368838</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>433254</t>
+          <t>430994</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>300516</t>
+          <t>301856</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362501</t>
+          <t>361561</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>688507</t>
+          <t>687184</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>778547</t>
+          <t>771348</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1850019</t>
+          <t>1844031</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1965044</t>
+          <t>1970458</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2409124</t>
+          <t>2401120</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2519358</t>
+          <t>2517117</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4292739</t>
+          <t>4284597</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4457638</t>
+          <t>4451431</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,73%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1461735</t>
+          <t>1456321</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1576760</t>
+          <t>1582748</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1038951</t>
+          <t>1041192</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1149185</t>
+          <t>1157189</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2527450</t>
+          <t>2533657</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2692349</t>
+          <t>2700491</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>331525</t>
+          <t>329844</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>385093</t>
+          <t>383568</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>415093</t>
+          <t>417043</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>465442</t>
+          <t>466636</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>762039</t>
+          <t>761759</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>835145</t>
+          <t>831993</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,74%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>289707</t>
+          <t>291232</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>343275</t>
+          <t>344956</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>207397</t>
+          <t>206203</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257746</t>
+          <t>255796</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>512494</t>
+          <t>515646</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>585600</t>
+          <t>585880</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,47%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>498445</t>
+          <t>497265</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>563291</t>
+          <t>561663</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>651986</t>
+          <t>650969</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>716049</t>
+          <t>713222</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1166354</t>
+          <t>1164641</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1256625</t>
+          <t>1251799</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,61%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>459140</t>
+          <t>460768</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>523986</t>
+          <t>525166</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>326864</t>
+          <t>329691</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>390927</t>
+          <t>391944</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>808719</t>
+          <t>813545</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>898990</t>
+          <t>900703</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,61%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>339964</t>
+          <t>336703</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>398466</t>
+          <t>397284</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>443761</t>
+          <t>441465</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>499972</t>
+          <t>498839</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>799650</t>
+          <t>799318</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>878556</t>
+          <t>878806</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,9%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>361086</t>
+          <t>362268</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>419588</t>
+          <t>422849</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>285039</t>
+          <t>286172</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>341250</t>
+          <t>343546</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>666007</t>
+          <t>665757</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>744913</t>
+          <t>745245</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,25%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>490550</t>
+          <t>490871</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>547475</t>
+          <t>548932</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>629484</t>
+          <t>632656</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>694785</t>
+          <t>696784</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1136241</t>
+          <t>1130949</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1222061</t>
+          <t>1224221</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,79%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>390092</t>
+          <t>388635</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>447017</t>
+          <t>446696</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348994</t>
+          <t>346995</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>414295</t>
+          <t>411123</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>759285</t>
+          <t>757125</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>845105</t>
+          <t>850397</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,92%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1714718</t>
+          <t>1708608</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1829476</t>
+          <t>1830690</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2204921</t>
+          <t>2200429</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2318325</t>
+          <t>2313834</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3954961</t>
+          <t>3947609</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4114052</t>
+          <t>4111313</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,25%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1564874</t>
+          <t>1563660</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1679632</t>
+          <t>1685742</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1226217</t>
+          <t>1230708</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1339621</t>
+          <t>1344113</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2824840</t>
+          <t>2827579</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2983931</t>
+          <t>2991283</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,11%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>284071</t>
+          <t>300935</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>258070</t>
+          <t>273749</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>313631</t>
+          <t>329227</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>330829</t>
+          <t>361177</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>261082</t>
+          <t>336852</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>363125</t>
+          <t>382817</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>614901</t>
+          <t>662112</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>541519</t>
+          <t>627636</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>656008</t>
+          <t>699053</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>49,06%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>351370</t>
+          <t>389775</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>321810</t>
+          <t>361483</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>377371</t>
+          <t>416961</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>394501</t>
+          <t>373003</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>362205</t>
+          <t>351363</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>464248</t>
+          <t>397328</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>745871</t>
+          <t>762777</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>704764</t>
+          <t>725836</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>819253</t>
+          <t>797253</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>55,95%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>391011</t>
+          <t>420519</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>181488</t>
+          <t>386435</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>503370</t>
+          <t>453953</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>473577</t>
+          <t>523631</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>447500</t>
+          <t>494917</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>502155</t>
+          <t>553149</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>864588</t>
+          <t>944150</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>576241</t>
+          <t>901380</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>987734</t>
+          <t>987527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,57%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>801853</t>
+          <t>628398</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>689494</t>
+          <t>594964</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1011376</t>
+          <t>662482</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>485074</t>
+          <t>547843</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>456496</t>
+          <t>518325</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511151</t>
+          <t>576557</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1286928</t>
+          <t>1176241</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1163782</t>
+          <t>1132864</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1575275</t>
+          <t>1219011</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>57,49%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>289201</t>
+          <t>318142</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>260277</t>
+          <t>287694</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>318375</t>
+          <t>353978</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>509113</t>
+          <t>347322</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>372261</t>
+          <t>322365</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>717153</t>
+          <t>372263</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>798314</t>
+          <t>665464</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>658842</t>
+          <t>625487</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1073526</t>
+          <t>708390</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>43,85%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>415479</t>
+          <t>484931</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>386305</t>
+          <t>449095</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>444403</t>
+          <t>515379</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>424253</t>
+          <t>464937</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>216213</t>
+          <t>439996</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>561105</t>
+          <t>489894</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>839732</t>
+          <t>949868</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>564520</t>
+          <t>906942</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>979204</t>
+          <t>989845</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>61,28%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>354490</t>
+          <t>358387</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>324603</t>
+          <t>328508</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>388349</t>
+          <t>391134</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>465298</t>
+          <t>496659</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>379906</t>
+          <t>467825</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>511462</t>
+          <t>523900</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>819789</t>
+          <t>855046</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>723580</t>
+          <t>817476</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>873317</t>
+          <t>899221</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,64%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>572341</t>
+          <t>631675</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>538482</t>
+          <t>598928</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>602228</t>
+          <t>661554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>629634</t>
+          <t>622382</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>583470</t>
+          <t>595141</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>715026</t>
+          <t>651216</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1201974</t>
+          <t>1254058</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1148446</t>
+          <t>1209883</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1298183</t>
+          <t>1291628</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>61,24%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1318774</t>
+          <t>1397982</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1022275</t>
+          <t>1339425</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1443659</t>
+          <t>1464117</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1778817</t>
+          <t>1728788</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1633608</t>
+          <t>1679038</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2158123</t>
+          <t>1785648</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3097592</t>
+          <t>3126771</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2822782</t>
+          <t>3042214</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3424282</t>
+          <t>3215997</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>44,24%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2141043</t>
+          <t>2134780</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2016158</t>
+          <t>2068645</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2437542</t>
+          <t>2193337</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1933463</t>
+          <t>2008166</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1554157</t>
+          <t>1951306</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2078672</t>
+          <t>2057916</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4074505</t>
+          <t>4142945</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3747815</t>
+          <t>4053719</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4349315</t>
+          <t>4227502</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>58,15%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna condición, enfermedad crónica o limitación en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna condición, enfermedad crónica o limitación en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna condición, enfermedad crónica o limitación en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna condición, enfermedad crónica o limitación en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
